--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076756</v>
       </c>
       <c r="B2" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127074941</v>
+        <v>127076668</v>
       </c>
       <c r="B3" t="n">
-        <v>78386</v>
+        <v>79629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607611</v>
+        <v>607787</v>
       </c>
       <c r="R3" t="n">
-        <v>7326390</v>
+        <v>7326543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127077017</v>
+        <v>127074941</v>
       </c>
       <c r="B4" t="n">
-        <v>79598</v>
+        <v>78417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607714</v>
+        <v>607611</v>
       </c>
       <c r="R4" t="n">
-        <v>7326595</v>
+        <v>7326390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127076668</v>
+        <v>127077017</v>
       </c>
       <c r="B5" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607787</v>
+        <v>607714</v>
       </c>
       <c r="R5" t="n">
-        <v>7326543</v>
+        <v>7326595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>127079280</v>
       </c>
       <c r="B6" t="n">
-        <v>91506</v>
+        <v>91580</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127074380</v>
+        <v>127078526</v>
       </c>
       <c r="B7" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607439</v>
+        <v>607630</v>
       </c>
       <c r="R7" t="n">
-        <v>7326243</v>
+        <v>7326801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127078526</v>
+        <v>127074380</v>
       </c>
       <c r="B8" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607630</v>
+        <v>607439</v>
       </c>
       <c r="R8" t="n">
-        <v>7326801</v>
+        <v>7326243</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>127074949</v>
       </c>
       <c r="B9" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127078636</v>
       </c>
       <c r="B10" t="n">
-        <v>91506</v>
+        <v>91580</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127078668</v>
       </c>
       <c r="B11" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127074251</v>
+        <v>127076330</v>
       </c>
       <c r="B12" t="n">
-        <v>105381</v>
+        <v>79629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607381</v>
+        <v>607710</v>
       </c>
       <c r="R12" t="n">
-        <v>7326163</v>
+        <v>7326472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127076330</v>
+        <v>127074251</v>
       </c>
       <c r="B13" t="n">
-        <v>79598</v>
+        <v>105456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607710</v>
+        <v>607381</v>
       </c>
       <c r="R13" t="n">
-        <v>7326472</v>
+        <v>7326163</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,45 +1839,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127074519</v>
+        <v>127075079</v>
       </c>
       <c r="B14" t="n">
-        <v>80119</v>
+        <v>57817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607517</v>
+        <v>607678</v>
       </c>
       <c r="R14" t="n">
-        <v>7326285</v>
+        <v>7326420</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1939,7 +1948,7 @@
         <v>127078508</v>
       </c>
       <c r="B15" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,54 +2042,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127075079</v>
+        <v>127074519</v>
       </c>
       <c r="B16" t="n">
-        <v>57817</v>
+        <v>80150</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607678</v>
+        <v>607517</v>
       </c>
       <c r="R16" t="n">
-        <v>7326420</v>
+        <v>7326285</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2142,7 +2142,7 @@
         <v>127079200</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>127076482</v>
       </c>
       <c r="B18" t="n">
-        <v>77929</v>
+        <v>77989</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>127078292</v>
       </c>
       <c r="B19" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>127078644</v>
       </c>
       <c r="B20" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>127078974</v>
       </c>
       <c r="B21" t="n">
-        <v>96614</v>
+        <v>96689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>127076452</v>
       </c>
       <c r="B22" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>127079093</v>
       </c>
       <c r="B23" t="n">
-        <v>105381</v>
+        <v>105456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,10 +2818,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127074359</v>
+        <v>127079154</v>
       </c>
       <c r="B24" t="n">
-        <v>57817</v>
+        <v>91337</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2829,39 +2829,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607418</v>
+        <v>607496</v>
       </c>
       <c r="R24" t="n">
-        <v>7326232</v>
+        <v>7326679</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,7 +2918,7 @@
         <v>127078849</v>
       </c>
       <c r="B25" t="n">
-        <v>91406</v>
+        <v>91480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127079154</v>
+        <v>127074359</v>
       </c>
       <c r="B26" t="n">
-        <v>91263</v>
+        <v>57817</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3028,34 +3023,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607496</v>
+        <v>607418</v>
       </c>
       <c r="R26" t="n">
-        <v>7326679</v>
+        <v>7326232</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127079706</v>
+        <v>127079568</v>
       </c>
       <c r="B27" t="n">
-        <v>91263</v>
+        <v>91319</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607423</v>
+        <v>607570</v>
       </c>
       <c r="R27" t="n">
-        <v>7326497</v>
+        <v>7326549</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,7 +3214,7 @@
         <v>127075134</v>
       </c>
       <c r="B28" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127079568</v>
+        <v>127076783</v>
       </c>
       <c r="B29" t="n">
-        <v>91245</v>
+        <v>91284</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607570</v>
+        <v>607730</v>
       </c>
       <c r="R29" t="n">
-        <v>7326549</v>
+        <v>7326604</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127076783</v>
+        <v>127079706</v>
       </c>
       <c r="B30" t="n">
-        <v>91210</v>
+        <v>91337</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607730</v>
+        <v>607423</v>
       </c>
       <c r="R30" t="n">
-        <v>7326604</v>
+        <v>7326497</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,7 +3505,7 @@
         <v>127078742</v>
       </c>
       <c r="B31" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>127079261</v>
       </c>
       <c r="B32" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127078504</v>
       </c>
       <c r="B33" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076756</v>
       </c>
       <c r="B2" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127076668</v>
       </c>
       <c r="B3" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127074941</v>
       </c>
       <c r="B4" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127077017</v>
       </c>
       <c r="B5" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127079280</v>
       </c>
       <c r="B6" t="n">
-        <v>91580</v>
+        <v>91586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127078526</v>
       </c>
       <c r="B7" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127074380</v>
       </c>
       <c r="B8" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127074949</v>
       </c>
       <c r="B9" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127078636</v>
       </c>
       <c r="B10" t="n">
-        <v>91580</v>
+        <v>91586</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127078668</v>
       </c>
       <c r="B11" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127076330</v>
       </c>
       <c r="B12" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127074251</v>
       </c>
       <c r="B13" t="n">
-        <v>105456</v>
+        <v>105462</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,32 +1945,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127078508</v>
+        <v>127074519</v>
       </c>
       <c r="B15" t="n">
-        <v>78678</v>
+        <v>80153</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607646</v>
+        <v>607517</v>
       </c>
       <c r="R15" t="n">
-        <v>7326785</v>
+        <v>7326285</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127074519</v>
+        <v>127079200</v>
       </c>
       <c r="B16" t="n">
-        <v>80150</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607517</v>
+        <v>607506</v>
       </c>
       <c r="R16" t="n">
-        <v>7326285</v>
+        <v>7326696</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127079200</v>
+        <v>127078508</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>78681</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607506</v>
+        <v>607646</v>
       </c>
       <c r="R17" t="n">
-        <v>7326696</v>
+        <v>7326785</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
         <v>127076482</v>
       </c>
       <c r="B18" t="n">
-        <v>77989</v>
+        <v>77992</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,45 +2333,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127078292</v>
+        <v>127078644</v>
       </c>
       <c r="B19" t="n">
-        <v>78678</v>
+        <v>92615</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607686</v>
+        <v>607586</v>
       </c>
       <c r="R19" t="n">
-        <v>7326705</v>
+        <v>7326861</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,45 +2430,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127078644</v>
+        <v>127078292</v>
       </c>
       <c r="B20" t="n">
-        <v>92609</v>
+        <v>78681</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607586</v>
+        <v>607686</v>
       </c>
       <c r="R20" t="n">
-        <v>7326861</v>
+        <v>7326705</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>127078974</v>
       </c>
       <c r="B21" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>127076452</v>
       </c>
       <c r="B22" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>127079093</v>
       </c>
       <c r="B23" t="n">
-        <v>105456</v>
+        <v>105462</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>127079154</v>
       </c>
       <c r="B24" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>127078849</v>
       </c>
       <c r="B25" t="n">
-        <v>91480</v>
+        <v>91486</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127079568</v>
+        <v>127075134</v>
       </c>
       <c r="B27" t="n">
-        <v>91319</v>
+        <v>79632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607570</v>
+        <v>607634</v>
       </c>
       <c r="R27" t="n">
-        <v>7326549</v>
+        <v>7326481</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127075134</v>
+        <v>127079706</v>
       </c>
       <c r="B28" t="n">
-        <v>79629</v>
+        <v>91343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607634</v>
+        <v>607423</v>
       </c>
       <c r="R28" t="n">
-        <v>7326481</v>
+        <v>7326497</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
         <v>127076783</v>
       </c>
       <c r="B29" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3405,45 +3405,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127079706</v>
+        <v>127078742</v>
       </c>
       <c r="B30" t="n">
-        <v>91337</v>
+        <v>92615</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607423</v>
+        <v>607552</v>
       </c>
       <c r="R30" t="n">
-        <v>7326497</v>
+        <v>7326830</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,45 +3502,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127078742</v>
+        <v>127079568</v>
       </c>
       <c r="B31" t="n">
-        <v>92609</v>
+        <v>91325</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607552</v>
+        <v>607570</v>
       </c>
       <c r="R31" t="n">
-        <v>7326830</v>
+        <v>7326549</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
         <v>127079261</v>
       </c>
       <c r="B32" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127078504</v>
       </c>
       <c r="B33" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127076668</v>
+        <v>127079280</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>91586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607787</v>
+        <v>607531</v>
       </c>
       <c r="R3" t="n">
-        <v>7326543</v>
+        <v>7326670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127074941</v>
+        <v>127076668</v>
       </c>
       <c r="B4" t="n">
-        <v>78420</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607611</v>
+        <v>607787</v>
       </c>
       <c r="R4" t="n">
-        <v>7326390</v>
+        <v>7326543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127077017</v>
+        <v>127074941</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>78420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607714</v>
+        <v>607611</v>
       </c>
       <c r="R5" t="n">
-        <v>7326595</v>
+        <v>7326390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127079280</v>
+        <v>127077017</v>
       </c>
       <c r="B6" t="n">
-        <v>91586</v>
+        <v>79632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607531</v>
+        <v>607714</v>
       </c>
       <c r="R6" t="n">
-        <v>7326670</v>
+        <v>7326595</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1945,32 +1945,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127074519</v>
+        <v>127078508</v>
       </c>
       <c r="B15" t="n">
-        <v>80153</v>
+        <v>78681</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607517</v>
+        <v>607646</v>
       </c>
       <c r="R15" t="n">
-        <v>7326285</v>
+        <v>7326785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127078508</v>
+        <v>127074519</v>
       </c>
       <c r="B17" t="n">
-        <v>78681</v>
+        <v>80153</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607646</v>
+        <v>607517</v>
       </c>
       <c r="R17" t="n">
-        <v>7326785</v>
+        <v>7326285</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2333,45 +2333,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127078644</v>
+        <v>127078292</v>
       </c>
       <c r="B19" t="n">
-        <v>92615</v>
+        <v>78681</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607586</v>
+        <v>607686</v>
       </c>
       <c r="R19" t="n">
-        <v>7326861</v>
+        <v>7326705</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,45 +2430,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127078292</v>
+        <v>127078644</v>
       </c>
       <c r="B20" t="n">
-        <v>78681</v>
+        <v>92615</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607686</v>
+        <v>607586</v>
       </c>
       <c r="R20" t="n">
-        <v>7326705</v>
+        <v>7326861</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076452</v>
+        <v>127079093</v>
       </c>
       <c r="B22" t="n">
-        <v>79632</v>
+        <v>105462</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607721</v>
+        <v>607489</v>
       </c>
       <c r="R22" t="n">
-        <v>7326477</v>
+        <v>7326681</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127079093</v>
+        <v>127076452</v>
       </c>
       <c r="B23" t="n">
-        <v>105462</v>
+        <v>79632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607489</v>
+        <v>607721</v>
       </c>
       <c r="R23" t="n">
-        <v>7326681</v>
+        <v>7326477</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,45 +2818,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127079154</v>
+        <v>127078849</v>
       </c>
       <c r="B24" t="n">
-        <v>91343</v>
+        <v>91486</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607496</v>
+        <v>607506</v>
       </c>
       <c r="R24" t="n">
-        <v>7326679</v>
+        <v>7326767</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,45 +2915,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127078849</v>
+        <v>127079154</v>
       </c>
       <c r="B25" t="n">
-        <v>91486</v>
+        <v>91343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607506</v>
+        <v>607496</v>
       </c>
       <c r="R25" t="n">
-        <v>7326767</v>
+        <v>7326679</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127075134</v>
+        <v>127079706</v>
       </c>
       <c r="B27" t="n">
-        <v>79632</v>
+        <v>91343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607634</v>
+        <v>607423</v>
       </c>
       <c r="R27" t="n">
-        <v>7326481</v>
+        <v>7326497</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,32 +3211,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127079706</v>
+        <v>127076783</v>
       </c>
       <c r="B28" t="n">
-        <v>91343</v>
+        <v>91290</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607423</v>
+        <v>607730</v>
       </c>
       <c r="R28" t="n">
-        <v>7326497</v>
+        <v>7326604</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127076783</v>
+        <v>127078742</v>
       </c>
       <c r="B29" t="n">
-        <v>91290</v>
+        <v>92615</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,34 +3319,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607730</v>
+        <v>607552</v>
       </c>
       <c r="R29" t="n">
-        <v>7326604</v>
+        <v>7326830</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,45 +3405,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127078742</v>
+        <v>127075134</v>
       </c>
       <c r="B30" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607552</v>
+        <v>607634</v>
       </c>
       <c r="R30" t="n">
-        <v>7326830</v>
+        <v>7326481</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127076330</v>
+        <v>127074251</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>105462</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607710</v>
+        <v>607381</v>
       </c>
       <c r="R12" t="n">
-        <v>7326472</v>
+        <v>7326163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127074251</v>
+        <v>127076330</v>
       </c>
       <c r="B13" t="n">
-        <v>105462</v>
+        <v>79632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607381</v>
+        <v>607710</v>
       </c>
       <c r="R13" t="n">
-        <v>7326163</v>
+        <v>7326472</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,54 +1839,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127075079</v>
+        <v>127074519</v>
       </c>
       <c r="B14" t="n">
-        <v>57817</v>
+        <v>80153</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607678</v>
+        <v>607517</v>
       </c>
       <c r="R14" t="n">
-        <v>7326420</v>
+        <v>7326285</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127078508</v>
+        <v>127075079</v>
       </c>
       <c r="B15" t="n">
-        <v>78681</v>
+        <v>57817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,34 +1947,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607646</v>
+        <v>607678</v>
       </c>
       <c r="R15" t="n">
-        <v>7326785</v>
+        <v>7326420</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127079200</v>
+        <v>127078508</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607506</v>
+        <v>607646</v>
       </c>
       <c r="R16" t="n">
-        <v>7326696</v>
+        <v>7326785</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127074519</v>
+        <v>127079200</v>
       </c>
       <c r="B17" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607517</v>
+        <v>607506</v>
       </c>
       <c r="R17" t="n">
-        <v>7326285</v>
+        <v>7326696</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127079093</v>
+        <v>127076452</v>
       </c>
       <c r="B22" t="n">
-        <v>105462</v>
+        <v>79632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607489</v>
+        <v>607721</v>
       </c>
       <c r="R22" t="n">
-        <v>7326681</v>
+        <v>7326477</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076452</v>
+        <v>127079093</v>
       </c>
       <c r="B23" t="n">
-        <v>79632</v>
+        <v>105462</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607721</v>
+        <v>607489</v>
       </c>
       <c r="R23" t="n">
-        <v>7326477</v>
+        <v>7326681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,45 +2818,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127078849</v>
+        <v>127074359</v>
       </c>
       <c r="B24" t="n">
-        <v>91486</v>
+        <v>57817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607506</v>
+        <v>607418</v>
       </c>
       <c r="R24" t="n">
-        <v>7326767</v>
+        <v>7326232</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3012,50 +3017,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127074359</v>
+        <v>127078849</v>
       </c>
       <c r="B26" t="n">
-        <v>57817</v>
+        <v>91486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607418</v>
+        <v>607506</v>
       </c>
       <c r="R26" t="n">
-        <v>7326232</v>
+        <v>7326767</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076756</v>
       </c>
       <c r="B2" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127079280</v>
+        <v>127074941</v>
       </c>
       <c r="B3" t="n">
-        <v>91586</v>
+        <v>78420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607531</v>
+        <v>607611</v>
       </c>
       <c r="R3" t="n">
-        <v>7326670</v>
+        <v>7326390</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127074941</v>
+        <v>127077017</v>
       </c>
       <c r="B5" t="n">
-        <v>78420</v>
+        <v>79632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607611</v>
+        <v>607714</v>
       </c>
       <c r="R5" t="n">
-        <v>7326390</v>
+        <v>7326595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127077017</v>
+        <v>127079280</v>
       </c>
       <c r="B6" t="n">
-        <v>79632</v>
+        <v>91587</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607714</v>
+        <v>607531</v>
       </c>
       <c r="R6" t="n">
-        <v>7326595</v>
+        <v>7326670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>127078636</v>
       </c>
       <c r="B10" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127074251</v>
+        <v>127076330</v>
       </c>
       <c r="B12" t="n">
-        <v>105462</v>
+        <v>79632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607381</v>
+        <v>607710</v>
       </c>
       <c r="R12" t="n">
-        <v>7326163</v>
+        <v>7326472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127076330</v>
+        <v>127074251</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>105463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607710</v>
+        <v>607381</v>
       </c>
       <c r="R13" t="n">
-        <v>7326472</v>
+        <v>7326163</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127075079</v>
+        <v>127079200</v>
       </c>
       <c r="B15" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,43 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607678</v>
+        <v>607506</v>
       </c>
       <c r="R15" t="n">
-        <v>7326420</v>
+        <v>7326696</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127079200</v>
+        <v>127075079</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,34 +2141,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607506</v>
+        <v>607678</v>
       </c>
       <c r="R17" t="n">
-        <v>7326696</v>
+        <v>7326420</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2333,45 +2333,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127078292</v>
+        <v>127078644</v>
       </c>
       <c r="B19" t="n">
-        <v>78681</v>
+        <v>92616</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607686</v>
+        <v>607586</v>
       </c>
       <c r="R19" t="n">
-        <v>7326705</v>
+        <v>7326861</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,45 +2430,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127078644</v>
+        <v>127078292</v>
       </c>
       <c r="B20" t="n">
-        <v>92615</v>
+        <v>78681</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607586</v>
+        <v>607686</v>
       </c>
       <c r="R20" t="n">
-        <v>7326861</v>
+        <v>7326705</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>127078974</v>
       </c>
       <c r="B21" t="n">
-        <v>96695</v>
+        <v>96696</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>127079093</v>
       </c>
       <c r="B23" t="n">
-        <v>105462</v>
+        <v>105463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,10 +2818,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127074359</v>
+        <v>127079154</v>
       </c>
       <c r="B24" t="n">
-        <v>57817</v>
+        <v>91344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2829,39 +2829,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607418</v>
+        <v>607496</v>
       </c>
       <c r="R24" t="n">
-        <v>7326232</v>
+        <v>7326679</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2920,45 +2915,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127079154</v>
+        <v>127078849</v>
       </c>
       <c r="B25" t="n">
-        <v>91343</v>
+        <v>91487</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607496</v>
+        <v>607506</v>
       </c>
       <c r="R25" t="n">
-        <v>7326679</v>
+        <v>7326767</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,45 +3012,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127078849</v>
+        <v>127074359</v>
       </c>
       <c r="B26" t="n">
-        <v>91486</v>
+        <v>57817</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607506</v>
+        <v>607418</v>
       </c>
       <c r="R26" t="n">
-        <v>7326767</v>
+        <v>7326232</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127079706</v>
+        <v>127075134</v>
       </c>
       <c r="B27" t="n">
-        <v>91343</v>
+        <v>79632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607423</v>
+        <v>607634</v>
       </c>
       <c r="R27" t="n">
-        <v>7326497</v>
+        <v>7326481</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,7 +3214,7 @@
         <v>127076783</v>
       </c>
       <c r="B28" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>127078742</v>
       </c>
       <c r="B29" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127075134</v>
+        <v>127079568</v>
       </c>
       <c r="B30" t="n">
-        <v>79632</v>
+        <v>91326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607634</v>
+        <v>607570</v>
       </c>
       <c r="R30" t="n">
-        <v>7326481</v>
+        <v>7326549</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127079568</v>
+        <v>127079706</v>
       </c>
       <c r="B31" t="n">
-        <v>91325</v>
+        <v>91344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607570</v>
+        <v>607423</v>
       </c>
       <c r="R31" t="n">
-        <v>7326549</v>
+        <v>7326497</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076452</v>
+        <v>127079093</v>
       </c>
       <c r="B22" t="n">
-        <v>79632</v>
+        <v>105463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607721</v>
+        <v>607489</v>
       </c>
       <c r="R22" t="n">
-        <v>7326477</v>
+        <v>7326681</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127079093</v>
+        <v>127076452</v>
       </c>
       <c r="B23" t="n">
-        <v>105463</v>
+        <v>79632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607489</v>
+        <v>607721</v>
       </c>
       <c r="R23" t="n">
-        <v>7326681</v>
+        <v>7326477</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127074941</v>
+        <v>127079280</v>
       </c>
       <c r="B3" t="n">
-        <v>78420</v>
+        <v>91587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607611</v>
+        <v>607531</v>
       </c>
       <c r="R3" t="n">
-        <v>7326390</v>
+        <v>7326670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127077017</v>
+        <v>127074941</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>78420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607714</v>
+        <v>607611</v>
       </c>
       <c r="R5" t="n">
-        <v>7326595</v>
+        <v>7326390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127079280</v>
+        <v>127077017</v>
       </c>
       <c r="B6" t="n">
-        <v>91587</v>
+        <v>79632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607531</v>
+        <v>607714</v>
       </c>
       <c r="R6" t="n">
-        <v>7326670</v>
+        <v>7326595</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127078526</v>
+        <v>127074380</v>
       </c>
       <c r="B7" t="n">
         <v>78420</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607630</v>
+        <v>607439</v>
       </c>
       <c r="R7" t="n">
-        <v>7326801</v>
+        <v>7326243</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127074380</v>
+        <v>127078526</v>
       </c>
       <c r="B8" t="n">
         <v>78420</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607439</v>
+        <v>607630</v>
       </c>
       <c r="R8" t="n">
-        <v>7326243</v>
+        <v>7326801</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127076330</v>
+        <v>127074251</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>105463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607710</v>
+        <v>607381</v>
       </c>
       <c r="R12" t="n">
-        <v>7326472</v>
+        <v>7326163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127074251</v>
+        <v>127076330</v>
       </c>
       <c r="B13" t="n">
-        <v>105463</v>
+        <v>79632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607381</v>
+        <v>607710</v>
       </c>
       <c r="R13" t="n">
-        <v>7326163</v>
+        <v>7326472</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,45 +1839,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127074519</v>
+        <v>127075079</v>
       </c>
       <c r="B14" t="n">
-        <v>80153</v>
+        <v>57817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607517</v>
+        <v>607678</v>
       </c>
       <c r="R14" t="n">
-        <v>7326285</v>
+        <v>7326420</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127079200</v>
+        <v>127078508</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607506</v>
+        <v>607646</v>
       </c>
       <c r="R15" t="n">
-        <v>7326696</v>
+        <v>7326785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127078508</v>
+        <v>127074519</v>
       </c>
       <c r="B16" t="n">
-        <v>78681</v>
+        <v>80153</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607646</v>
+        <v>607517</v>
       </c>
       <c r="R16" t="n">
-        <v>7326785</v>
+        <v>7326285</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127075079</v>
+        <v>127079200</v>
       </c>
       <c r="B17" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,43 +2150,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607678</v>
+        <v>607506</v>
       </c>
       <c r="R17" t="n">
-        <v>7326420</v>
+        <v>7326696</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2333,45 +2333,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127078644</v>
+        <v>127078292</v>
       </c>
       <c r="B19" t="n">
-        <v>92616</v>
+        <v>78681</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607586</v>
+        <v>607686</v>
       </c>
       <c r="R19" t="n">
-        <v>7326861</v>
+        <v>7326705</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,45 +2430,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127078292</v>
+        <v>127078644</v>
       </c>
       <c r="B20" t="n">
-        <v>78681</v>
+        <v>92616</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607686</v>
+        <v>607586</v>
       </c>
       <c r="R20" t="n">
-        <v>7326705</v>
+        <v>7326861</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127079093</v>
+        <v>127076452</v>
       </c>
       <c r="B22" t="n">
-        <v>105463</v>
+        <v>79632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607489</v>
+        <v>607721</v>
       </c>
       <c r="R22" t="n">
-        <v>7326681</v>
+        <v>7326477</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076452</v>
+        <v>127079093</v>
       </c>
       <c r="B23" t="n">
-        <v>79632</v>
+        <v>105463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607721</v>
+        <v>607489</v>
       </c>
       <c r="R23" t="n">
-        <v>7326477</v>
+        <v>7326681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,45 +2818,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127079154</v>
+        <v>127078849</v>
       </c>
       <c r="B24" t="n">
-        <v>91344</v>
+        <v>91487</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607496</v>
+        <v>607506</v>
       </c>
       <c r="R24" t="n">
-        <v>7326679</v>
+        <v>7326767</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,45 +2915,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127078849</v>
+        <v>127079154</v>
       </c>
       <c r="B25" t="n">
-        <v>91487</v>
+        <v>91344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607506</v>
+        <v>607496</v>
       </c>
       <c r="R25" t="n">
-        <v>7326767</v>
+        <v>7326679</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127075134</v>
+        <v>127079568</v>
       </c>
       <c r="B27" t="n">
-        <v>79632</v>
+        <v>91326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607634</v>
+        <v>607570</v>
       </c>
       <c r="R27" t="n">
-        <v>7326481</v>
+        <v>7326549</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,32 +3211,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127076783</v>
+        <v>127075134</v>
       </c>
       <c r="B28" t="n">
-        <v>91291</v>
+        <v>79632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607730</v>
+        <v>607634</v>
       </c>
       <c r="R28" t="n">
-        <v>7326604</v>
+        <v>7326481</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127078742</v>
+        <v>127076783</v>
       </c>
       <c r="B29" t="n">
-        <v>92616</v>
+        <v>91291</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,34 +3319,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607552</v>
+        <v>607730</v>
       </c>
       <c r="R29" t="n">
-        <v>7326830</v>
+        <v>7326604</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127079568</v>
+        <v>127079706</v>
       </c>
       <c r="B30" t="n">
-        <v>91326</v>
+        <v>91344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607570</v>
+        <v>607423</v>
       </c>
       <c r="R30" t="n">
-        <v>7326549</v>
+        <v>7326497</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,45 +3502,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127079706</v>
+        <v>127078742</v>
       </c>
       <c r="B31" t="n">
-        <v>91344</v>
+        <v>92616</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607423</v>
+        <v>607552</v>
       </c>
       <c r="R31" t="n">
-        <v>7326497</v>
+        <v>7326830</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127074380</v>
+        <v>127078526</v>
       </c>
       <c r="B7" t="n">
         <v>78420</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607439</v>
+        <v>607630</v>
       </c>
       <c r="R7" t="n">
-        <v>7326243</v>
+        <v>7326801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127078526</v>
+        <v>127074380</v>
       </c>
       <c r="B8" t="n">
         <v>78420</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607630</v>
+        <v>607439</v>
       </c>
       <c r="R8" t="n">
-        <v>7326801</v>
+        <v>7326243</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127074251</v>
+        <v>127076330</v>
       </c>
       <c r="B12" t="n">
-        <v>105463</v>
+        <v>79632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607381</v>
+        <v>607710</v>
       </c>
       <c r="R12" t="n">
-        <v>7326163</v>
+        <v>7326472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127076330</v>
+        <v>127074251</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>105463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607710</v>
+        <v>607381</v>
       </c>
       <c r="R13" t="n">
-        <v>7326472</v>
+        <v>7326163</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,54 +1839,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127075079</v>
+        <v>127074519</v>
       </c>
       <c r="B14" t="n">
-        <v>57817</v>
+        <v>80153</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607678</v>
+        <v>607517</v>
       </c>
       <c r="R14" t="n">
-        <v>7326420</v>
+        <v>7326285</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127078508</v>
+        <v>127079200</v>
       </c>
       <c r="B15" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607646</v>
+        <v>607506</v>
       </c>
       <c r="R15" t="n">
-        <v>7326785</v>
+        <v>7326696</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,45 +2033,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127074519</v>
+        <v>127075079</v>
       </c>
       <c r="B16" t="n">
-        <v>80153</v>
+        <v>57817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607517</v>
+        <v>607678</v>
       </c>
       <c r="R16" t="n">
-        <v>7326285</v>
+        <v>7326420</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127079200</v>
+        <v>127078508</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607506</v>
+        <v>607646</v>
       </c>
       <c r="R17" t="n">
-        <v>7326696</v>
+        <v>7326785</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127076330</v>
+        <v>127074251</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>105463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607710</v>
+        <v>607381</v>
       </c>
       <c r="R12" t="n">
-        <v>7326472</v>
+        <v>7326163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127074251</v>
+        <v>127076330</v>
       </c>
       <c r="B13" t="n">
-        <v>105463</v>
+        <v>79632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607381</v>
+        <v>607710</v>
       </c>
       <c r="R13" t="n">
-        <v>7326163</v>
+        <v>7326472</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,45 +1839,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127074519</v>
+        <v>127075079</v>
       </c>
       <c r="B14" t="n">
-        <v>80153</v>
+        <v>57817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607517</v>
+        <v>607678</v>
       </c>
       <c r="R14" t="n">
-        <v>7326285</v>
+        <v>7326420</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127079200</v>
+        <v>127078508</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607506</v>
+        <v>607646</v>
       </c>
       <c r="R15" t="n">
-        <v>7326696</v>
+        <v>7326785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,54 +2042,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127075079</v>
+        <v>127074519</v>
       </c>
       <c r="B16" t="n">
-        <v>57817</v>
+        <v>80153</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607678</v>
+        <v>607517</v>
       </c>
       <c r="R16" t="n">
-        <v>7326420</v>
+        <v>7326285</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127078508</v>
+        <v>127079200</v>
       </c>
       <c r="B17" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607646</v>
+        <v>607506</v>
       </c>
       <c r="R17" t="n">
-        <v>7326785</v>
+        <v>7326696</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127079568</v>
+        <v>127075134</v>
       </c>
       <c r="B27" t="n">
-        <v>91326</v>
+        <v>79632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607570</v>
+        <v>607634</v>
       </c>
       <c r="R27" t="n">
-        <v>7326549</v>
+        <v>7326481</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127075134</v>
+        <v>127079706</v>
       </c>
       <c r="B28" t="n">
-        <v>79632</v>
+        <v>91344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607634</v>
+        <v>607423</v>
       </c>
       <c r="R28" t="n">
-        <v>7326481</v>
+        <v>7326497</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3405,45 +3405,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127079706</v>
+        <v>127078742</v>
       </c>
       <c r="B30" t="n">
-        <v>91344</v>
+        <v>92616</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607423</v>
+        <v>607552</v>
       </c>
       <c r="R30" t="n">
-        <v>7326497</v>
+        <v>7326830</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,45 +3502,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127078742</v>
+        <v>127079568</v>
       </c>
       <c r="B31" t="n">
-        <v>92616</v>
+        <v>91326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607552</v>
+        <v>607570</v>
       </c>
       <c r="R31" t="n">
-        <v>7326830</v>
+        <v>7326549</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076756</v>
       </c>
       <c r="B2" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127079280</v>
       </c>
       <c r="B3" t="n">
-        <v>91587</v>
+        <v>91591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127076668</v>
+        <v>127074941</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>78424</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607787</v>
+        <v>607611</v>
       </c>
       <c r="R4" t="n">
-        <v>7326543</v>
+        <v>7326390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127074941</v>
+        <v>127077017</v>
       </c>
       <c r="B5" t="n">
-        <v>78420</v>
+        <v>79636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607611</v>
+        <v>607714</v>
       </c>
       <c r="R5" t="n">
-        <v>7326390</v>
+        <v>7326595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127077017</v>
+        <v>127076668</v>
       </c>
       <c r="B6" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607714</v>
+        <v>607787</v>
       </c>
       <c r="R6" t="n">
-        <v>7326595</v>
+        <v>7326543</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127078526</v>
+        <v>127074380</v>
       </c>
       <c r="B7" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607630</v>
+        <v>607439</v>
       </c>
       <c r="R7" t="n">
-        <v>7326801</v>
+        <v>7326243</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127074380</v>
+        <v>127078526</v>
       </c>
       <c r="B8" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607439</v>
+        <v>607630</v>
       </c>
       <c r="R8" t="n">
-        <v>7326243</v>
+        <v>7326801</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>127074949</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127078636</v>
       </c>
       <c r="B10" t="n">
-        <v>91587</v>
+        <v>91591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127078668</v>
       </c>
       <c r="B11" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127074251</v>
+        <v>127076330</v>
       </c>
       <c r="B12" t="n">
-        <v>105463</v>
+        <v>79636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607381</v>
+        <v>607710</v>
       </c>
       <c r="R12" t="n">
-        <v>7326163</v>
+        <v>7326472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127076330</v>
+        <v>127074251</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>105469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607710</v>
+        <v>607381</v>
       </c>
       <c r="R13" t="n">
-        <v>7326472</v>
+        <v>7326163</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
         <v>127075079</v>
       </c>
       <c r="B14" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>127078508</v>
       </c>
       <c r="B15" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127074519</v>
+        <v>127079200</v>
       </c>
       <c r="B16" t="n">
-        <v>80153</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607517</v>
+        <v>607506</v>
       </c>
       <c r="R16" t="n">
-        <v>7326285</v>
+        <v>7326696</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127079200</v>
+        <v>127074519</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>80157</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607506</v>
+        <v>607517</v>
       </c>
       <c r="R17" t="n">
-        <v>7326696</v>
+        <v>7326285</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
         <v>127076482</v>
       </c>
       <c r="B18" t="n">
-        <v>77992</v>
+        <v>77996</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,45 +2333,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127078292</v>
+        <v>127078644</v>
       </c>
       <c r="B19" t="n">
-        <v>78681</v>
+        <v>92620</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607686</v>
+        <v>607586</v>
       </c>
       <c r="R19" t="n">
-        <v>7326705</v>
+        <v>7326861</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,45 +2430,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127078644</v>
+        <v>127078292</v>
       </c>
       <c r="B20" t="n">
-        <v>92616</v>
+        <v>78685</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607586</v>
+        <v>607686</v>
       </c>
       <c r="R20" t="n">
-        <v>7326861</v>
+        <v>7326705</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>127078974</v>
       </c>
       <c r="B21" t="n">
-        <v>96696</v>
+        <v>96700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>127076452</v>
       </c>
       <c r="B22" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>127079093</v>
       </c>
       <c r="B23" t="n">
-        <v>105463</v>
+        <v>105469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>127078849</v>
       </c>
       <c r="B24" t="n">
-        <v>91487</v>
+        <v>91491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>127079154</v>
       </c>
       <c r="B25" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>127074359</v>
       </c>
       <c r="B26" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3114,45 +3114,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127075134</v>
+        <v>127078742</v>
       </c>
       <c r="B27" t="n">
-        <v>79632</v>
+        <v>92620</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607634</v>
+        <v>607552</v>
       </c>
       <c r="R27" t="n">
-        <v>7326481</v>
+        <v>7326830</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,7 +3214,7 @@
         <v>127079706</v>
       </c>
       <c r="B28" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127076783</v>
+        <v>127075134</v>
       </c>
       <c r="B29" t="n">
-        <v>91291</v>
+        <v>79636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607730</v>
+        <v>607634</v>
       </c>
       <c r="R29" t="n">
-        <v>7326604</v>
+        <v>7326481</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127078742</v>
+        <v>127076783</v>
       </c>
       <c r="B30" t="n">
-        <v>92616</v>
+        <v>91295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,34 +3416,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607552</v>
+        <v>607730</v>
       </c>
       <c r="R30" t="n">
-        <v>7326830</v>
+        <v>7326604</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,7 +3505,7 @@
         <v>127079568</v>
       </c>
       <c r="B31" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127079261</v>
+        <v>127078504</v>
       </c>
       <c r="B32" t="n">
-        <v>79632</v>
+        <v>79607</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607534</v>
+        <v>607646</v>
       </c>
       <c r="R32" t="n">
-        <v>7326663</v>
+        <v>7326785</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127078504</v>
+        <v>127079261</v>
       </c>
       <c r="B33" t="n">
-        <v>79603</v>
+        <v>79636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>607646</v>
+        <v>607534</v>
       </c>
       <c r="R33" t="n">
-        <v>7326785</v>
+        <v>7326663</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127079280</v>
+        <v>127076668</v>
       </c>
       <c r="B3" t="n">
-        <v>91591</v>
+        <v>79636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607531</v>
+        <v>607787</v>
       </c>
       <c r="R3" t="n">
-        <v>7326670</v>
+        <v>7326543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127076668</v>
+        <v>127079280</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>91591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607787</v>
+        <v>607531</v>
       </c>
       <c r="R6" t="n">
-        <v>7326543</v>
+        <v>7326670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127074380</v>
+        <v>127078526</v>
       </c>
       <c r="B7" t="n">
         <v>78424</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607439</v>
+        <v>607630</v>
       </c>
       <c r="R7" t="n">
-        <v>7326243</v>
+        <v>7326801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127078526</v>
+        <v>127074380</v>
       </c>
       <c r="B8" t="n">
         <v>78424</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607630</v>
+        <v>607439</v>
       </c>
       <c r="R8" t="n">
-        <v>7326801</v>
+        <v>7326243</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127076330</v>
+        <v>127074251</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>105469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607710</v>
+        <v>607381</v>
       </c>
       <c r="R12" t="n">
-        <v>7326472</v>
+        <v>7326163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127074251</v>
+        <v>127076330</v>
       </c>
       <c r="B13" t="n">
-        <v>105469</v>
+        <v>79636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607381</v>
+        <v>607710</v>
       </c>
       <c r="R13" t="n">
-        <v>7326163</v>
+        <v>7326472</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,54 +1839,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127075079</v>
+        <v>127074519</v>
       </c>
       <c r="B14" t="n">
-        <v>57821</v>
+        <v>80157</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607678</v>
+        <v>607517</v>
       </c>
       <c r="R14" t="n">
-        <v>7326420</v>
+        <v>7326285</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127078508</v>
+        <v>127079200</v>
       </c>
       <c r="B15" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607646</v>
+        <v>607506</v>
       </c>
       <c r="R15" t="n">
-        <v>7326785</v>
+        <v>7326696</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127079200</v>
+        <v>127078508</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607506</v>
+        <v>607646</v>
       </c>
       <c r="R16" t="n">
-        <v>7326696</v>
+        <v>7326785</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,45 +2130,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127074519</v>
+        <v>127075079</v>
       </c>
       <c r="B17" t="n">
-        <v>80157</v>
+        <v>57821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607517</v>
+        <v>607678</v>
       </c>
       <c r="R17" t="n">
-        <v>7326285</v>
+        <v>7326420</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076452</v>
+        <v>127079093</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>105469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607721</v>
+        <v>607489</v>
       </c>
       <c r="R22" t="n">
-        <v>7326477</v>
+        <v>7326681</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127079093</v>
+        <v>127076452</v>
       </c>
       <c r="B23" t="n">
-        <v>105469</v>
+        <v>79636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607489</v>
+        <v>607721</v>
       </c>
       <c r="R23" t="n">
-        <v>7326681</v>
+        <v>7326477</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,45 +2818,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127078849</v>
+        <v>127074359</v>
       </c>
       <c r="B24" t="n">
-        <v>91491</v>
+        <v>57821</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607506</v>
+        <v>607418</v>
       </c>
       <c r="R24" t="n">
-        <v>7326767</v>
+        <v>7326232</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,45 +2920,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127079154</v>
+        <v>127078849</v>
       </c>
       <c r="B25" t="n">
-        <v>91348</v>
+        <v>91491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607496</v>
+        <v>607506</v>
       </c>
       <c r="R25" t="n">
-        <v>7326679</v>
+        <v>7326767</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127074359</v>
+        <v>127079154</v>
       </c>
       <c r="B26" t="n">
-        <v>57821</v>
+        <v>91348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,39 +3028,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607418</v>
+        <v>607496</v>
       </c>
       <c r="R26" t="n">
-        <v>7326232</v>
+        <v>7326679</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127075134</v>
+        <v>127076783</v>
       </c>
       <c r="B29" t="n">
-        <v>79636</v>
+        <v>91295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607634</v>
+        <v>607730</v>
       </c>
       <c r="R29" t="n">
-        <v>7326481</v>
+        <v>7326604</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127076783</v>
+        <v>127079568</v>
       </c>
       <c r="B30" t="n">
-        <v>91295</v>
+        <v>91330</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607730</v>
+        <v>607570</v>
       </c>
       <c r="R30" t="n">
-        <v>7326604</v>
+        <v>7326549</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127079568</v>
+        <v>127075134</v>
       </c>
       <c r="B31" t="n">
-        <v>91330</v>
+        <v>79636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607570</v>
+        <v>607634</v>
       </c>
       <c r="R31" t="n">
-        <v>7326549</v>
+        <v>7326481</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127078504</v>
+        <v>127079261</v>
       </c>
       <c r="B32" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607646</v>
+        <v>607534</v>
       </c>
       <c r="R32" t="n">
-        <v>7326785</v>
+        <v>7326663</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127079261</v>
+        <v>127078504</v>
       </c>
       <c r="B33" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>607534</v>
+        <v>607646</v>
       </c>
       <c r="R33" t="n">
-        <v>7326663</v>
+        <v>7326785</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127074251</v>
+        <v>127076330</v>
       </c>
       <c r="B12" t="n">
-        <v>105469</v>
+        <v>79636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607381</v>
+        <v>607710</v>
       </c>
       <c r="R12" t="n">
-        <v>7326163</v>
+        <v>7326472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127076330</v>
+        <v>127074251</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>105469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607710</v>
+        <v>607381</v>
       </c>
       <c r="R13" t="n">
-        <v>7326472</v>
+        <v>7326163</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2818,50 +2818,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127074359</v>
+        <v>127078849</v>
       </c>
       <c r="B24" t="n">
-        <v>57821</v>
+        <v>91491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607418</v>
+        <v>607506</v>
       </c>
       <c r="R24" t="n">
-        <v>7326232</v>
+        <v>7326767</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2920,45 +2915,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127078849</v>
+        <v>127079154</v>
       </c>
       <c r="B25" t="n">
-        <v>91491</v>
+        <v>91348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607506</v>
+        <v>607496</v>
       </c>
       <c r="R25" t="n">
-        <v>7326767</v>
+        <v>7326679</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127079154</v>
+        <v>127074359</v>
       </c>
       <c r="B26" t="n">
-        <v>91348</v>
+        <v>57821</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3028,34 +3023,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607496</v>
+        <v>607418</v>
       </c>
       <c r="R26" t="n">
-        <v>7326679</v>
+        <v>7326232</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -2818,45 +2818,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127078849</v>
+        <v>127074359</v>
       </c>
       <c r="B24" t="n">
-        <v>91491</v>
+        <v>57821</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607506</v>
+        <v>607418</v>
       </c>
       <c r="R24" t="n">
-        <v>7326767</v>
+        <v>7326232</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,45 +2920,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127079154</v>
+        <v>127078849</v>
       </c>
       <c r="B25" t="n">
-        <v>91348</v>
+        <v>91491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607496</v>
+        <v>607506</v>
       </c>
       <c r="R25" t="n">
-        <v>7326679</v>
+        <v>7326767</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127074359</v>
+        <v>127079154</v>
       </c>
       <c r="B26" t="n">
-        <v>57821</v>
+        <v>91348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,39 +3028,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607418</v>
+        <v>607496</v>
       </c>
       <c r="R26" t="n">
-        <v>7326232</v>
+        <v>7326679</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127076330</v>
+        <v>127074251</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>105471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607710</v>
+        <v>607381</v>
       </c>
       <c r="R12" t="n">
-        <v>7326472</v>
+        <v>7326163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127074251</v>
+        <v>127076330</v>
       </c>
       <c r="B13" t="n">
-        <v>105469</v>
+        <v>79636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607381</v>
+        <v>607710</v>
       </c>
       <c r="R13" t="n">
-        <v>7326163</v>
+        <v>7326472</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127074519</v>
+        <v>127078508</v>
       </c>
       <c r="B14" t="n">
-        <v>80157</v>
+        <v>78685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607517</v>
+        <v>607646</v>
       </c>
       <c r="R14" t="n">
-        <v>7326285</v>
+        <v>7326785</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127079200</v>
+        <v>127074519</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607506</v>
+        <v>607517</v>
       </c>
       <c r="R15" t="n">
-        <v>7326696</v>
+        <v>7326285</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127078508</v>
+        <v>127079200</v>
       </c>
       <c r="B16" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607646</v>
+        <v>607506</v>
       </c>
       <c r="R16" t="n">
-        <v>7326785</v>
+        <v>7326696</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,45 +2333,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127078644</v>
+        <v>127078292</v>
       </c>
       <c r="B19" t="n">
-        <v>92620</v>
+        <v>78685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607586</v>
+        <v>607686</v>
       </c>
       <c r="R19" t="n">
-        <v>7326861</v>
+        <v>7326705</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,45 +2430,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127078292</v>
+        <v>127078644</v>
       </c>
       <c r="B20" t="n">
-        <v>78685</v>
+        <v>92620</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607686</v>
+        <v>607586</v>
       </c>
       <c r="R20" t="n">
-        <v>7326705</v>
+        <v>7326861</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,7 +2627,7 @@
         <v>127079093</v>
       </c>
       <c r="B22" t="n">
-        <v>105469</v>
+        <v>105471</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2818,50 +2818,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127074359</v>
+        <v>127078849</v>
       </c>
       <c r="B24" t="n">
-        <v>57821</v>
+        <v>91491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607418</v>
+        <v>607506</v>
       </c>
       <c r="R24" t="n">
-        <v>7326232</v>
+        <v>7326767</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2920,45 +2915,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127078849</v>
+        <v>127079154</v>
       </c>
       <c r="B25" t="n">
-        <v>91491</v>
+        <v>91348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607506</v>
+        <v>607496</v>
       </c>
       <c r="R25" t="n">
-        <v>7326767</v>
+        <v>7326679</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127079154</v>
+        <v>127074359</v>
       </c>
       <c r="B26" t="n">
-        <v>91348</v>
+        <v>57821</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3028,34 +3023,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607496</v>
+        <v>607418</v>
       </c>
       <c r="R26" t="n">
-        <v>7326679</v>
+        <v>7326232</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,45 +3114,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127078742</v>
+        <v>127079568</v>
       </c>
       <c r="B27" t="n">
-        <v>92620</v>
+        <v>91330</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607552</v>
+        <v>607570</v>
       </c>
       <c r="R27" t="n">
-        <v>7326830</v>
+        <v>7326549</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127079706</v>
+        <v>127075134</v>
       </c>
       <c r="B28" t="n">
-        <v>91348</v>
+        <v>79636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607423</v>
+        <v>607634</v>
       </c>
       <c r="R28" t="n">
-        <v>7326497</v>
+        <v>7326481</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127076783</v>
+        <v>127079706</v>
       </c>
       <c r="B29" t="n">
-        <v>91295</v>
+        <v>91348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607730</v>
+        <v>607423</v>
       </c>
       <c r="R29" t="n">
-        <v>7326604</v>
+        <v>7326497</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127079568</v>
+        <v>127076783</v>
       </c>
       <c r="B30" t="n">
-        <v>91330</v>
+        <v>91295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607570</v>
+        <v>607730</v>
       </c>
       <c r="R30" t="n">
-        <v>7326549</v>
+        <v>7326604</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,45 +3502,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127075134</v>
+        <v>127078742</v>
       </c>
       <c r="B31" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607634</v>
+        <v>607552</v>
       </c>
       <c r="R31" t="n">
-        <v>7326481</v>
+        <v>7326830</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127074251</v>
+        <v>127076330</v>
       </c>
       <c r="B12" t="n">
-        <v>105471</v>
+        <v>79636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607381</v>
+        <v>607710</v>
       </c>
       <c r="R12" t="n">
-        <v>7326163</v>
+        <v>7326472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127076330</v>
+        <v>127074251</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>105471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607710</v>
+        <v>607381</v>
       </c>
       <c r="R13" t="n">
-        <v>7326472</v>
+        <v>7326163</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127079093</v>
+        <v>127076452</v>
       </c>
       <c r="B22" t="n">
-        <v>105471</v>
+        <v>79636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607489</v>
+        <v>607721</v>
       </c>
       <c r="R22" t="n">
-        <v>7326681</v>
+        <v>7326477</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076452</v>
+        <v>127079093</v>
       </c>
       <c r="B23" t="n">
-        <v>79636</v>
+        <v>105471</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607721</v>
+        <v>607489</v>
       </c>
       <c r="R23" t="n">
-        <v>7326477</v>
+        <v>7326681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127079154</v>
+        <v>127074359</v>
       </c>
       <c r="B25" t="n">
-        <v>91348</v>
+        <v>57821</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2926,34 +2926,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607496</v>
+        <v>607418</v>
       </c>
       <c r="R25" t="n">
-        <v>7326679</v>
+        <v>7326232</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127074359</v>
+        <v>127079154</v>
       </c>
       <c r="B26" t="n">
-        <v>57821</v>
+        <v>91348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,39 +3028,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607418</v>
+        <v>607496</v>
       </c>
       <c r="R26" t="n">
-        <v>7326232</v>
+        <v>7326679</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076756</v>
       </c>
       <c r="B2" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127076668</v>
+        <v>127079280</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>91593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607787</v>
+        <v>607531</v>
       </c>
       <c r="R3" t="n">
-        <v>7326543</v>
+        <v>7326670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127074941</v>
+        <v>127076668</v>
       </c>
       <c r="B4" t="n">
-        <v>78424</v>
+        <v>79638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607611</v>
+        <v>607787</v>
       </c>
       <c r="R4" t="n">
-        <v>7326390</v>
+        <v>7326543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127077017</v>
+        <v>127074941</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>78426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607714</v>
+        <v>607611</v>
       </c>
       <c r="R5" t="n">
-        <v>7326595</v>
+        <v>7326390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127079280</v>
+        <v>127077017</v>
       </c>
       <c r="B6" t="n">
-        <v>91591</v>
+        <v>79638</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607531</v>
+        <v>607714</v>
       </c>
       <c r="R6" t="n">
-        <v>7326670</v>
+        <v>7326595</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127078526</v>
       </c>
       <c r="B7" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127074380</v>
       </c>
       <c r="B8" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127074949</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127078636</v>
       </c>
       <c r="B10" t="n">
-        <v>91591</v>
+        <v>91593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127078668</v>
       </c>
       <c r="B11" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127076330</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127074251</v>
       </c>
       <c r="B13" t="n">
-        <v>105471</v>
+        <v>105473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127078508</v>
+        <v>127079200</v>
       </c>
       <c r="B14" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607646</v>
+        <v>607506</v>
       </c>
       <c r="R14" t="n">
-        <v>7326785</v>
+        <v>7326696</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1939,7 +1939,7 @@
         <v>127074519</v>
       </c>
       <c r="B15" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127079200</v>
+        <v>127078508</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>78687</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607506</v>
+        <v>607646</v>
       </c>
       <c r="R16" t="n">
-        <v>7326696</v>
+        <v>7326785</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>127075079</v>
       </c>
       <c r="B17" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>127076482</v>
       </c>
       <c r="B18" t="n">
-        <v>77996</v>
+        <v>77998</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,45 +2333,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127078292</v>
+        <v>127078644</v>
       </c>
       <c r="B19" t="n">
-        <v>78685</v>
+        <v>92622</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607686</v>
+        <v>607586</v>
       </c>
       <c r="R19" t="n">
-        <v>7326705</v>
+        <v>7326861</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,45 +2430,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127078644</v>
+        <v>127078292</v>
       </c>
       <c r="B20" t="n">
-        <v>92620</v>
+        <v>78687</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607586</v>
+        <v>607686</v>
       </c>
       <c r="R20" t="n">
-        <v>7326861</v>
+        <v>7326705</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>127078974</v>
       </c>
       <c r="B21" t="n">
-        <v>96700</v>
+        <v>96702</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>127076452</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>127079093</v>
       </c>
       <c r="B23" t="n">
-        <v>105471</v>
+        <v>105473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>127078849</v>
       </c>
       <c r="B24" t="n">
-        <v>91491</v>
+        <v>91493</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127074359</v>
+        <v>127079154</v>
       </c>
       <c r="B25" t="n">
-        <v>57821</v>
+        <v>91350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2926,39 +2926,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607418</v>
+        <v>607496</v>
       </c>
       <c r="R25" t="n">
-        <v>7326232</v>
+        <v>7326679</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127079154</v>
+        <v>127074359</v>
       </c>
       <c r="B26" t="n">
-        <v>91348</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3028,34 +3023,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607496</v>
+        <v>607418</v>
       </c>
       <c r="R26" t="n">
-        <v>7326679</v>
+        <v>7326232</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127079568</v>
+        <v>127075134</v>
       </c>
       <c r="B27" t="n">
-        <v>91330</v>
+        <v>79638</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607570</v>
+        <v>607634</v>
       </c>
       <c r="R27" t="n">
-        <v>7326549</v>
+        <v>7326481</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127075134</v>
+        <v>127079568</v>
       </c>
       <c r="B28" t="n">
-        <v>79636</v>
+        <v>91332</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607634</v>
+        <v>607570</v>
       </c>
       <c r="R28" t="n">
-        <v>7326481</v>
+        <v>7326549</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,45 +3308,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127079706</v>
+        <v>127078742</v>
       </c>
       <c r="B29" t="n">
-        <v>91348</v>
+        <v>92622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607423</v>
+        <v>607552</v>
       </c>
       <c r="R29" t="n">
-        <v>7326497</v>
+        <v>7326830</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127076783</v>
+        <v>127079706</v>
       </c>
       <c r="B30" t="n">
-        <v>91295</v>
+        <v>91350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607730</v>
+        <v>607423</v>
       </c>
       <c r="R30" t="n">
-        <v>7326604</v>
+        <v>7326497</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127078742</v>
+        <v>127076783</v>
       </c>
       <c r="B31" t="n">
-        <v>92620</v>
+        <v>91297</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,34 +3513,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607552</v>
+        <v>607730</v>
       </c>
       <c r="R31" t="n">
-        <v>7326830</v>
+        <v>7326604</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127079261</v>
+        <v>127078504</v>
       </c>
       <c r="B32" t="n">
-        <v>79636</v>
+        <v>79609</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607534</v>
+        <v>607646</v>
       </c>
       <c r="R32" t="n">
-        <v>7326663</v>
+        <v>7326785</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127078504</v>
+        <v>127079261</v>
       </c>
       <c r="B33" t="n">
-        <v>79607</v>
+        <v>79638</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>607646</v>
+        <v>607534</v>
       </c>
       <c r="R33" t="n">
-        <v>7326785</v>
+        <v>7326663</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127076330</v>
+        <v>127074251</v>
       </c>
       <c r="B12" t="n">
-        <v>79638</v>
+        <v>105473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607710</v>
+        <v>607381</v>
       </c>
       <c r="R12" t="n">
-        <v>7326472</v>
+        <v>7326163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127074251</v>
+        <v>127076330</v>
       </c>
       <c r="B13" t="n">
-        <v>105473</v>
+        <v>79638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607381</v>
+        <v>607710</v>
       </c>
       <c r="R13" t="n">
-        <v>7326163</v>
+        <v>7326472</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127079200</v>
+        <v>127078508</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607506</v>
+        <v>607646</v>
       </c>
       <c r="R14" t="n">
-        <v>7326696</v>
+        <v>7326785</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,45 +1936,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127074519</v>
+        <v>127075079</v>
       </c>
       <c r="B15" t="n">
-        <v>80159</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607517</v>
+        <v>607678</v>
       </c>
       <c r="R15" t="n">
-        <v>7326285</v>
+        <v>7326420</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127078508</v>
+        <v>127079200</v>
       </c>
       <c r="B16" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607646</v>
+        <v>607506</v>
       </c>
       <c r="R16" t="n">
-        <v>7326785</v>
+        <v>7326696</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,54 +2139,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127075079</v>
+        <v>127074519</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>80159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607678</v>
+        <v>607517</v>
       </c>
       <c r="R17" t="n">
-        <v>7326420</v>
+        <v>7326285</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2818,45 +2818,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127078849</v>
+        <v>127079154</v>
       </c>
       <c r="B24" t="n">
-        <v>91493</v>
+        <v>91350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607506</v>
+        <v>607496</v>
       </c>
       <c r="R24" t="n">
-        <v>7326767</v>
+        <v>7326679</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,45 +2915,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127079154</v>
+        <v>127078849</v>
       </c>
       <c r="B25" t="n">
-        <v>91350</v>
+        <v>91493</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607496</v>
+        <v>607506</v>
       </c>
       <c r="R25" t="n">
-        <v>7326679</v>
+        <v>7326767</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127075134</v>
+        <v>127079568</v>
       </c>
       <c r="B27" t="n">
-        <v>79638</v>
+        <v>91332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607634</v>
+        <v>607570</v>
       </c>
       <c r="R27" t="n">
-        <v>7326481</v>
+        <v>7326549</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127079568</v>
+        <v>127079706</v>
       </c>
       <c r="B28" t="n">
-        <v>91332</v>
+        <v>91350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607570</v>
+        <v>607423</v>
       </c>
       <c r="R28" t="n">
-        <v>7326549</v>
+        <v>7326497</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127078742</v>
+        <v>127076783</v>
       </c>
       <c r="B29" t="n">
-        <v>92622</v>
+        <v>91297</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,34 +3319,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607552</v>
+        <v>607730</v>
       </c>
       <c r="R29" t="n">
-        <v>7326830</v>
+        <v>7326604</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,45 +3405,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127079706</v>
+        <v>127078742</v>
       </c>
       <c r="B30" t="n">
-        <v>91350</v>
+        <v>92622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607423</v>
+        <v>607552</v>
       </c>
       <c r="R30" t="n">
-        <v>7326497</v>
+        <v>7326830</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,32 +3502,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127076783</v>
+        <v>127075134</v>
       </c>
       <c r="B31" t="n">
-        <v>91297</v>
+        <v>79638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607730</v>
+        <v>607634</v>
       </c>
       <c r="R31" t="n">
-        <v>7326604</v>
+        <v>7326481</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127078504</v>
+        <v>127079261</v>
       </c>
       <c r="B32" t="n">
-        <v>79609</v>
+        <v>79638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607646</v>
+        <v>607534</v>
       </c>
       <c r="R32" t="n">
-        <v>7326785</v>
+        <v>7326663</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127079261</v>
+        <v>127078504</v>
       </c>
       <c r="B33" t="n">
-        <v>79638</v>
+        <v>79609</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>607534</v>
+        <v>607646</v>
       </c>
       <c r="R33" t="n">
-        <v>7326663</v>
+        <v>7326785</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127074251</v>
+        <v>127076330</v>
       </c>
       <c r="B12" t="n">
-        <v>105473</v>
+        <v>79638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607381</v>
+        <v>607710</v>
       </c>
       <c r="R12" t="n">
-        <v>7326163</v>
+        <v>7326472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127076330</v>
+        <v>127074251</v>
       </c>
       <c r="B13" t="n">
-        <v>79638</v>
+        <v>105473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607710</v>
+        <v>607381</v>
       </c>
       <c r="R13" t="n">
-        <v>7326472</v>
+        <v>7326163</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127078508</v>
+        <v>127074519</v>
       </c>
       <c r="B14" t="n">
-        <v>78687</v>
+        <v>80159</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607646</v>
+        <v>607517</v>
       </c>
       <c r="R14" t="n">
-        <v>7326785</v>
+        <v>7326285</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127075079</v>
+        <v>127079200</v>
       </c>
       <c r="B15" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,43 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607678</v>
+        <v>607506</v>
       </c>
       <c r="R15" t="n">
-        <v>7326420</v>
+        <v>7326696</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127079200</v>
+        <v>127078508</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607506</v>
+        <v>607646</v>
       </c>
       <c r="R16" t="n">
-        <v>7326696</v>
+        <v>7326785</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,45 +2130,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127074519</v>
+        <v>127075079</v>
       </c>
       <c r="B17" t="n">
-        <v>80159</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607517</v>
+        <v>607678</v>
       </c>
       <c r="R17" t="n">
-        <v>7326285</v>
+        <v>7326420</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2333,45 +2333,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127078644</v>
+        <v>127078292</v>
       </c>
       <c r="B19" t="n">
-        <v>92622</v>
+        <v>78687</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607586</v>
+        <v>607686</v>
       </c>
       <c r="R19" t="n">
-        <v>7326861</v>
+        <v>7326705</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,45 +2430,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127078292</v>
+        <v>127078644</v>
       </c>
       <c r="B20" t="n">
-        <v>78687</v>
+        <v>92622</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607686</v>
+        <v>607586</v>
       </c>
       <c r="R20" t="n">
-        <v>7326705</v>
+        <v>7326861</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2915,45 +2915,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127078849</v>
+        <v>127074359</v>
       </c>
       <c r="B25" t="n">
-        <v>91493</v>
+        <v>57823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607506</v>
+        <v>607418</v>
       </c>
       <c r="R25" t="n">
-        <v>7326767</v>
+        <v>7326232</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,50 +3017,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127074359</v>
+        <v>127078849</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>91493</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607418</v>
+        <v>607506</v>
       </c>
       <c r="R26" t="n">
-        <v>7326232</v>
+        <v>7326767</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127079706</v>
+        <v>127075134</v>
       </c>
       <c r="B28" t="n">
-        <v>91350</v>
+        <v>79638</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607423</v>
+        <v>607634</v>
       </c>
       <c r="R28" t="n">
-        <v>7326497</v>
+        <v>7326481</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127076783</v>
+        <v>127079706</v>
       </c>
       <c r="B29" t="n">
-        <v>91297</v>
+        <v>91350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607730</v>
+        <v>607423</v>
       </c>
       <c r="R29" t="n">
-        <v>7326604</v>
+        <v>7326497</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127078742</v>
+        <v>127076783</v>
       </c>
       <c r="B30" t="n">
-        <v>92622</v>
+        <v>91297</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,34 +3416,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607552</v>
+        <v>607730</v>
       </c>
       <c r="R30" t="n">
-        <v>7326830</v>
+        <v>7326604</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,45 +3502,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127075134</v>
+        <v>127078742</v>
       </c>
       <c r="B31" t="n">
-        <v>79638</v>
+        <v>92622</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607634</v>
+        <v>607552</v>
       </c>
       <c r="R31" t="n">
-        <v>7326481</v>
+        <v>7326830</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127079261</v>
+        <v>127078504</v>
       </c>
       <c r="B32" t="n">
-        <v>79638</v>
+        <v>79609</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607534</v>
+        <v>607646</v>
       </c>
       <c r="R32" t="n">
-        <v>7326663</v>
+        <v>7326785</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127078504</v>
+        <v>127079261</v>
       </c>
       <c r="B33" t="n">
-        <v>79609</v>
+        <v>79638</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>607646</v>
+        <v>607534</v>
       </c>
       <c r="R33" t="n">
-        <v>7326785</v>
+        <v>7326663</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076756</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127079280</v>
+        <v>127076668</v>
       </c>
       <c r="B3" t="n">
-        <v>91593</v>
+        <v>79638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607531</v>
+        <v>607787</v>
       </c>
       <c r="R3" t="n">
-        <v>7326670</v>
+        <v>7326543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127076668</v>
+        <v>127074941</v>
       </c>
       <c r="B4" t="n">
-        <v>79638</v>
+        <v>78426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607787</v>
+        <v>607611</v>
       </c>
       <c r="R4" t="n">
-        <v>7326543</v>
+        <v>7326390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127074941</v>
+        <v>127077017</v>
       </c>
       <c r="B5" t="n">
-        <v>78426</v>
+        <v>79638</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607611</v>
+        <v>607714</v>
       </c>
       <c r="R5" t="n">
-        <v>7326390</v>
+        <v>7326595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127077017</v>
+        <v>127079280</v>
       </c>
       <c r="B6" t="n">
-        <v>79638</v>
+        <v>91599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607714</v>
+        <v>607531</v>
       </c>
       <c r="R6" t="n">
-        <v>7326595</v>
+        <v>7326670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>127078636</v>
       </c>
       <c r="B10" t="n">
-        <v>91593</v>
+        <v>91599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127074251</v>
       </c>
       <c r="B13" t="n">
-        <v>105473</v>
+        <v>105479</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,45 +1839,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127074519</v>
+        <v>127075079</v>
       </c>
       <c r="B14" t="n">
-        <v>80159</v>
+        <v>57823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607517</v>
+        <v>607678</v>
       </c>
       <c r="R14" t="n">
-        <v>7326285</v>
+        <v>7326420</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127078508</v>
+        <v>127074519</v>
       </c>
       <c r="B16" t="n">
-        <v>78687</v>
+        <v>80159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607646</v>
+        <v>607517</v>
       </c>
       <c r="R16" t="n">
-        <v>7326785</v>
+        <v>7326285</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127075079</v>
+        <v>127078508</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>78687</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,43 +2150,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607678</v>
+        <v>607646</v>
       </c>
       <c r="R17" t="n">
-        <v>7326420</v>
+        <v>7326785</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,7 +2433,7 @@
         <v>127078644</v>
       </c>
       <c r="B20" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>127078974</v>
       </c>
       <c r="B21" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076452</v>
+        <v>127079093</v>
       </c>
       <c r="B22" t="n">
-        <v>79638</v>
+        <v>105479</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607721</v>
+        <v>607489</v>
       </c>
       <c r="R22" t="n">
-        <v>7326477</v>
+        <v>7326681</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127079093</v>
+        <v>127076452</v>
       </c>
       <c r="B23" t="n">
-        <v>105473</v>
+        <v>79638</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607489</v>
+        <v>607721</v>
       </c>
       <c r="R23" t="n">
-        <v>7326681</v>
+        <v>7326477</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2821,7 +2821,7 @@
         <v>127079154</v>
       </c>
       <c r="B24" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2915,50 +2915,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127074359</v>
+        <v>127078849</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>91499</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607418</v>
+        <v>607506</v>
       </c>
       <c r="R25" t="n">
-        <v>7326232</v>
+        <v>7326767</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,45 +3012,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127078849</v>
+        <v>127074359</v>
       </c>
       <c r="B26" t="n">
-        <v>91493</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607506</v>
+        <v>607418</v>
       </c>
       <c r="R26" t="n">
-        <v>7326767</v>
+        <v>7326232</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127079568</v>
+        <v>127075134</v>
       </c>
       <c r="B27" t="n">
-        <v>91332</v>
+        <v>79638</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607570</v>
+        <v>607634</v>
       </c>
       <c r="R27" t="n">
-        <v>7326549</v>
+        <v>7326481</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127075134</v>
+        <v>127079568</v>
       </c>
       <c r="B28" t="n">
-        <v>79638</v>
+        <v>91338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607634</v>
+        <v>607570</v>
       </c>
       <c r="R28" t="n">
-        <v>7326481</v>
+        <v>7326549</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
         <v>127079706</v>
       </c>
       <c r="B29" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>127076783</v>
       </c>
       <c r="B30" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>127078742</v>
       </c>
       <c r="B31" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076756</v>
       </c>
       <c r="B2" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127076668</v>
+        <v>127079280</v>
       </c>
       <c r="B3" t="n">
-        <v>79638</v>
+        <v>91602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607787</v>
+        <v>607531</v>
       </c>
       <c r="R3" t="n">
-        <v>7326543</v>
+        <v>7326670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127074941</v>
+        <v>127076668</v>
       </c>
       <c r="B4" t="n">
-        <v>78426</v>
+        <v>79641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607611</v>
+        <v>607787</v>
       </c>
       <c r="R4" t="n">
-        <v>7326390</v>
+        <v>7326543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127077017</v>
+        <v>127074941</v>
       </c>
       <c r="B5" t="n">
-        <v>79638</v>
+        <v>78429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607714</v>
+        <v>607611</v>
       </c>
       <c r="R5" t="n">
-        <v>7326595</v>
+        <v>7326390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127079280</v>
+        <v>127077017</v>
       </c>
       <c r="B6" t="n">
-        <v>91599</v>
+        <v>79641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607531</v>
+        <v>607714</v>
       </c>
       <c r="R6" t="n">
-        <v>7326670</v>
+        <v>7326595</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127078526</v>
       </c>
       <c r="B7" t="n">
-        <v>78426</v>
+        <v>78429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127074380</v>
       </c>
       <c r="B8" t="n">
-        <v>78426</v>
+        <v>78429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127074949</v>
       </c>
       <c r="B9" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127078636</v>
       </c>
       <c r="B10" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127078668</v>
       </c>
       <c r="B11" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127076330</v>
       </c>
       <c r="B12" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127074251</v>
       </c>
       <c r="B13" t="n">
-        <v>105479</v>
+        <v>105482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,54 +1839,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127075079</v>
+        <v>127074519</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>80162</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607678</v>
+        <v>607517</v>
       </c>
       <c r="R14" t="n">
-        <v>7326420</v>
+        <v>7326285</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,7 +1939,7 @@
         <v>127079200</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,45 +2033,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127074519</v>
+        <v>127075079</v>
       </c>
       <c r="B16" t="n">
-        <v>80159</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607517</v>
+        <v>607678</v>
       </c>
       <c r="R16" t="n">
-        <v>7326285</v>
+        <v>7326420</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2142,7 +2142,7 @@
         <v>127078508</v>
       </c>
       <c r="B17" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>127076482</v>
       </c>
       <c r="B18" t="n">
-        <v>77998</v>
+        <v>78001</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,45 +2333,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127078292</v>
+        <v>127078644</v>
       </c>
       <c r="B19" t="n">
-        <v>78687</v>
+        <v>92631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607686</v>
+        <v>607586</v>
       </c>
       <c r="R19" t="n">
-        <v>7326705</v>
+        <v>7326861</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,45 +2430,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127078644</v>
+        <v>127078292</v>
       </c>
       <c r="B20" t="n">
-        <v>92628</v>
+        <v>78690</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607586</v>
+        <v>607686</v>
       </c>
       <c r="R20" t="n">
-        <v>7326861</v>
+        <v>7326705</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>127078974</v>
       </c>
       <c r="B21" t="n">
-        <v>96708</v>
+        <v>96711</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127079093</v>
+        <v>127076452</v>
       </c>
       <c r="B22" t="n">
-        <v>105479</v>
+        <v>79641</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607489</v>
+        <v>607721</v>
       </c>
       <c r="R22" t="n">
-        <v>7326681</v>
+        <v>7326477</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076452</v>
+        <v>127079093</v>
       </c>
       <c r="B23" t="n">
-        <v>79638</v>
+        <v>105482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607721</v>
+        <v>607489</v>
       </c>
       <c r="R23" t="n">
-        <v>7326477</v>
+        <v>7326681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,45 +2818,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127079154</v>
+        <v>127078849</v>
       </c>
       <c r="B24" t="n">
-        <v>91356</v>
+        <v>91502</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607496</v>
+        <v>607506</v>
       </c>
       <c r="R24" t="n">
-        <v>7326679</v>
+        <v>7326767</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,45 +2915,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127078849</v>
+        <v>127079154</v>
       </c>
       <c r="B25" t="n">
-        <v>91499</v>
+        <v>91359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607506</v>
+        <v>607496</v>
       </c>
       <c r="R25" t="n">
-        <v>7326767</v>
+        <v>7326679</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
         <v>127074359</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>127075134</v>
       </c>
       <c r="B27" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>127079568</v>
       </c>
       <c r="B28" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>127079706</v>
       </c>
       <c r="B29" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>127076783</v>
       </c>
       <c r="B30" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>127078742</v>
       </c>
       <c r="B31" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>127078504</v>
       </c>
       <c r="B32" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127079261</v>
       </c>
       <c r="B33" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3791,6 +3791,434 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128364511</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>607494</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7326402</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128364543</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78437</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>607627</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7326556</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128364532</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79110</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>864</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>607627</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7326556</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128364510</v>
+      </c>
+      <c r="B37" t="n">
+        <v>96725</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>53</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>607558</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7326436</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -3796,7 +3796,7 @@
         <v>128364511</v>
       </c>
       <c r="B34" t="n">
-        <v>79649</v>
+        <v>79650</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128364543</v>
       </c>
       <c r="B35" t="n">
-        <v>78437</v>
+        <v>78438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>128364532</v>
       </c>
       <c r="B36" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>128364510</v>
       </c>
       <c r="B37" t="n">
-        <v>96725</v>
+        <v>96730</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -3796,7 +3796,7 @@
         <v>128364511</v>
       </c>
       <c r="B34" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128364543</v>
       </c>
       <c r="B35" t="n">
-        <v>78438</v>
+        <v>78486</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>128364532</v>
       </c>
       <c r="B36" t="n">
-        <v>79111</v>
+        <v>79162</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>128364510</v>
       </c>
       <c r="B37" t="n">
-        <v>96730</v>
+        <v>96823</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -3796,7 +3796,7 @@
         <v>128364511</v>
       </c>
       <c r="B34" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128364543</v>
       </c>
       <c r="B35" t="n">
-        <v>78486</v>
+        <v>78490</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>128364532</v>
       </c>
       <c r="B36" t="n">
-        <v>79162</v>
+        <v>79166</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>128364510</v>
       </c>
       <c r="B37" t="n">
-        <v>96823</v>
+        <v>96835</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -3796,7 +3796,7 @@
         <v>128364511</v>
       </c>
       <c r="B34" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128364543</v>
       </c>
       <c r="B35" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>128364532</v>
       </c>
       <c r="B36" t="n">
-        <v>79166</v>
+        <v>79168</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>128364510</v>
       </c>
       <c r="B37" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4117,7 +4117,7 @@
         <v>128364510</v>
       </c>
       <c r="B37" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -3796,7 +3796,7 @@
         <v>128364511</v>
       </c>
       <c r="B34" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128364543</v>
       </c>
       <c r="B35" t="n">
-        <v>78492</v>
+        <v>78519</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>128364532</v>
       </c>
       <c r="B36" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>128364510</v>
       </c>
       <c r="B37" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4219,6 +4219,212 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129188285</v>
+      </c>
+      <c r="B38" t="n">
+        <v>83003</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>308</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tjiärmadahkka, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>607624</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7326586</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129188674</v>
+      </c>
+      <c r="B39" t="n">
+        <v>56913</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tjiärmadahkka , Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>607648</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7326543</v>
+      </c>
+      <c r="S39" t="n">
+        <v>50</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4425,6 +4425,223 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129211120</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Tjiärmadahkka , Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>607735</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7326535</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129211232</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Tjiärmadahkka , Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>607765</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7326469</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4427,10 +4427,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129211120</v>
+        <v>129211232</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4466,10 +4466,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>607735</v>
+        <v>607765</v>
       </c>
       <c r="R40" t="n">
-        <v>7326535</v>
+        <v>7326469</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4499,9 +4499,24 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4525,122 +4540,6 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>129211232</v>
-      </c>
-      <c r="B41" t="n">
-        <v>57723</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Tjiärmadahkka , Pi lm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>607765</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7326469</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4224,7 +4224,7 @@
         <v>129188285</v>
       </c>
       <c r="B38" t="n">
-        <v>83003</v>
+        <v>83007</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>129188674</v>
       </c>
       <c r="B39" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4224,7 +4224,7 @@
         <v>129188285</v>
       </c>
       <c r="B38" t="n">
-        <v>83007</v>
+        <v>82997</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4224,7 +4224,7 @@
         <v>129188285</v>
       </c>
       <c r="B38" t="n">
-        <v>82997</v>
+        <v>82999</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>129188674</v>
       </c>
       <c r="B39" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>129211232</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4224,7 +4224,7 @@
         <v>129188285</v>
       </c>
       <c r="B38" t="n">
-        <v>82999</v>
+        <v>83003</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4224,7 +4224,7 @@
         <v>129188285</v>
       </c>
       <c r="B38" t="n">
-        <v>83003</v>
+        <v>83004</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4224,7 +4224,7 @@
         <v>129188285</v>
       </c>
       <c r="B38" t="n">
-        <v>83004</v>
+        <v>83031</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>129188674</v>
       </c>
       <c r="B39" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>129211232</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4430,7 +4430,7 @@
         <v>129211232</v>
       </c>
       <c r="B40" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076756</v>
       </c>
       <c r="B2" t="n">
-        <v>91359</v>
+        <v>91337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127079280</v>
+        <v>127076668</v>
       </c>
       <c r="B3" t="n">
-        <v>91602</v>
+        <v>79629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607531</v>
+        <v>607787</v>
       </c>
       <c r="R3" t="n">
-        <v>7326670</v>
+        <v>7326543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127076668</v>
+        <v>127074941</v>
       </c>
       <c r="B4" t="n">
-        <v>79641</v>
+        <v>78417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607787</v>
+        <v>607611</v>
       </c>
       <c r="R4" t="n">
-        <v>7326543</v>
+        <v>7326390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127074941</v>
+        <v>127077017</v>
       </c>
       <c r="B5" t="n">
-        <v>78429</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607611</v>
+        <v>607714</v>
       </c>
       <c r="R5" t="n">
-        <v>7326390</v>
+        <v>7326595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127077017</v>
+        <v>127079280</v>
       </c>
       <c r="B6" t="n">
-        <v>79641</v>
+        <v>91580</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607714</v>
+        <v>607531</v>
       </c>
       <c r="R6" t="n">
-        <v>7326595</v>
+        <v>7326670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127078526</v>
       </c>
       <c r="B7" t="n">
-        <v>78429</v>
+        <v>78417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127074380</v>
       </c>
       <c r="B8" t="n">
-        <v>78429</v>
+        <v>78417</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127074949</v>
       </c>
       <c r="B9" t="n">
-        <v>79641</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127078636</v>
       </c>
       <c r="B10" t="n">
-        <v>91602</v>
+        <v>91580</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127078668</v>
       </c>
       <c r="B11" t="n">
-        <v>78690</v>
+        <v>78678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127076330</v>
       </c>
       <c r="B12" t="n">
-        <v>79641</v>
+        <v>79629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127074251</v>
       </c>
       <c r="B13" t="n">
-        <v>105482</v>
+        <v>105456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,45 +1839,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127074519</v>
+        <v>127075079</v>
       </c>
       <c r="B14" t="n">
-        <v>80162</v>
+        <v>57817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607517</v>
+        <v>607678</v>
       </c>
       <c r="R14" t="n">
-        <v>7326285</v>
+        <v>7326420</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127079200</v>
+        <v>127078508</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>78678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607506</v>
+        <v>607646</v>
       </c>
       <c r="R15" t="n">
-        <v>7326696</v>
+        <v>7326785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,54 +2042,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127075079</v>
+        <v>127074519</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>80150</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607678</v>
+        <v>607517</v>
       </c>
       <c r="R16" t="n">
-        <v>7326420</v>
+        <v>7326285</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127078508</v>
+        <v>127079200</v>
       </c>
       <c r="B17" t="n">
-        <v>78690</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607646</v>
+        <v>607506</v>
       </c>
       <c r="R17" t="n">
-        <v>7326785</v>
+        <v>7326696</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
         <v>127076482</v>
       </c>
       <c r="B18" t="n">
-        <v>78001</v>
+        <v>77989</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,45 +2333,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127078644</v>
+        <v>127078292</v>
       </c>
       <c r="B19" t="n">
-        <v>92631</v>
+        <v>78678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607586</v>
+        <v>607686</v>
       </c>
       <c r="R19" t="n">
-        <v>7326861</v>
+        <v>7326705</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,45 +2430,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127078292</v>
+        <v>127078644</v>
       </c>
       <c r="B20" t="n">
-        <v>78690</v>
+        <v>92609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607686</v>
+        <v>607586</v>
       </c>
       <c r="R20" t="n">
-        <v>7326705</v>
+        <v>7326861</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>127078974</v>
       </c>
       <c r="B21" t="n">
-        <v>96711</v>
+        <v>96689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>127076452</v>
       </c>
       <c r="B22" t="n">
-        <v>79641</v>
+        <v>79629</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>127079093</v>
       </c>
       <c r="B23" t="n">
-        <v>105482</v>
+        <v>105456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,45 +2818,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127078849</v>
+        <v>127079154</v>
       </c>
       <c r="B24" t="n">
-        <v>91502</v>
+        <v>91337</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607506</v>
+        <v>607496</v>
       </c>
       <c r="R24" t="n">
-        <v>7326767</v>
+        <v>7326679</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,45 +2915,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127079154</v>
+        <v>127078849</v>
       </c>
       <c r="B25" t="n">
-        <v>91359</v>
+        <v>91480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607496</v>
+        <v>607506</v>
       </c>
       <c r="R25" t="n">
-        <v>7326679</v>
+        <v>7326767</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
         <v>127074359</v>
       </c>
       <c r="B26" t="n">
-        <v>57826</v>
+        <v>57817</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127075134</v>
+        <v>127079568</v>
       </c>
       <c r="B27" t="n">
-        <v>79641</v>
+        <v>91319</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607634</v>
+        <v>607570</v>
       </c>
       <c r="R27" t="n">
-        <v>7326481</v>
+        <v>7326549</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127079568</v>
+        <v>127075134</v>
       </c>
       <c r="B28" t="n">
-        <v>91341</v>
+        <v>79629</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607570</v>
+        <v>607634</v>
       </c>
       <c r="R28" t="n">
-        <v>7326549</v>
+        <v>7326481</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127079706</v>
+        <v>127076783</v>
       </c>
       <c r="B29" t="n">
-        <v>91359</v>
+        <v>91284</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607423</v>
+        <v>607730</v>
       </c>
       <c r="R29" t="n">
-        <v>7326497</v>
+        <v>7326604</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127076783</v>
+        <v>127079706</v>
       </c>
       <c r="B30" t="n">
-        <v>91306</v>
+        <v>91337</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607730</v>
+        <v>607423</v>
       </c>
       <c r="R30" t="n">
-        <v>7326604</v>
+        <v>7326497</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,7 +3505,7 @@
         <v>127078742</v>
       </c>
       <c r="B31" t="n">
-        <v>92631</v>
+        <v>92609</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127078504</v>
+        <v>127079261</v>
       </c>
       <c r="B32" t="n">
-        <v>79612</v>
+        <v>79629</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607646</v>
+        <v>607534</v>
       </c>
       <c r="R32" t="n">
-        <v>7326785</v>
+        <v>7326663</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127079261</v>
+        <v>127078504</v>
       </c>
       <c r="B33" t="n">
-        <v>79641</v>
+        <v>79600</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>607534</v>
+        <v>607646</v>
       </c>
       <c r="R33" t="n">
-        <v>7326663</v>
+        <v>7326785</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076756</v>
       </c>
       <c r="B2" t="n">
-        <v>91337</v>
+        <v>91359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127076668</v>
+        <v>127079280</v>
       </c>
       <c r="B3" t="n">
-        <v>79629</v>
+        <v>91602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607787</v>
+        <v>607531</v>
       </c>
       <c r="R3" t="n">
-        <v>7326543</v>
+        <v>7326670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127074941</v>
+        <v>127076668</v>
       </c>
       <c r="B4" t="n">
-        <v>78417</v>
+        <v>79641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607611</v>
+        <v>607787</v>
       </c>
       <c r="R4" t="n">
-        <v>7326390</v>
+        <v>7326543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127077017</v>
+        <v>127074941</v>
       </c>
       <c r="B5" t="n">
-        <v>79629</v>
+        <v>78429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607714</v>
+        <v>607611</v>
       </c>
       <c r="R5" t="n">
-        <v>7326595</v>
+        <v>7326390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127079280</v>
+        <v>127077017</v>
       </c>
       <c r="B6" t="n">
-        <v>91580</v>
+        <v>79641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607531</v>
+        <v>607714</v>
       </c>
       <c r="R6" t="n">
-        <v>7326670</v>
+        <v>7326595</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127078526</v>
       </c>
       <c r="B7" t="n">
-        <v>78417</v>
+        <v>78429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127074380</v>
       </c>
       <c r="B8" t="n">
-        <v>78417</v>
+        <v>78429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127074949</v>
       </c>
       <c r="B9" t="n">
-        <v>79629</v>
+        <v>79641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127078636</v>
       </c>
       <c r="B10" t="n">
-        <v>91580</v>
+        <v>91602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127078668</v>
       </c>
       <c r="B11" t="n">
-        <v>78678</v>
+        <v>78690</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127076330</v>
       </c>
       <c r="B12" t="n">
-        <v>79629</v>
+        <v>79641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127074251</v>
       </c>
       <c r="B13" t="n">
-        <v>105456</v>
+        <v>105482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,54 +1839,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127075079</v>
+        <v>127074519</v>
       </c>
       <c r="B14" t="n">
-        <v>57817</v>
+        <v>80162</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607678</v>
+        <v>607517</v>
       </c>
       <c r="R14" t="n">
-        <v>7326420</v>
+        <v>7326285</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127078508</v>
+        <v>127079200</v>
       </c>
       <c r="B15" t="n">
-        <v>78678</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607646</v>
+        <v>607506</v>
       </c>
       <c r="R15" t="n">
-        <v>7326785</v>
+        <v>7326696</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,45 +2033,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127074519</v>
+        <v>127075079</v>
       </c>
       <c r="B16" t="n">
-        <v>80150</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607517</v>
+        <v>607678</v>
       </c>
       <c r="R16" t="n">
-        <v>7326285</v>
+        <v>7326420</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127079200</v>
+        <v>127078508</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>78690</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607506</v>
+        <v>607646</v>
       </c>
       <c r="R17" t="n">
-        <v>7326696</v>
+        <v>7326785</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
         <v>127076482</v>
       </c>
       <c r="B18" t="n">
-        <v>77989</v>
+        <v>78001</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,45 +2333,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127078292</v>
+        <v>127078644</v>
       </c>
       <c r="B19" t="n">
-        <v>78678</v>
+        <v>92631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607686</v>
+        <v>607586</v>
       </c>
       <c r="R19" t="n">
-        <v>7326705</v>
+        <v>7326861</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,45 +2430,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127078644</v>
+        <v>127078292</v>
       </c>
       <c r="B20" t="n">
-        <v>92609</v>
+        <v>78690</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607586</v>
+        <v>607686</v>
       </c>
       <c r="R20" t="n">
-        <v>7326861</v>
+        <v>7326705</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>127078974</v>
       </c>
       <c r="B21" t="n">
-        <v>96689</v>
+        <v>96711</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>127076452</v>
       </c>
       <c r="B22" t="n">
-        <v>79629</v>
+        <v>79641</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>127079093</v>
       </c>
       <c r="B23" t="n">
-        <v>105456</v>
+        <v>105482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,45 +2818,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127079154</v>
+        <v>127078849</v>
       </c>
       <c r="B24" t="n">
-        <v>91337</v>
+        <v>91502</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607496</v>
+        <v>607506</v>
       </c>
       <c r="R24" t="n">
-        <v>7326679</v>
+        <v>7326767</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,45 +2915,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127078849</v>
+        <v>127079154</v>
       </c>
       <c r="B25" t="n">
-        <v>91480</v>
+        <v>91359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607506</v>
+        <v>607496</v>
       </c>
       <c r="R25" t="n">
-        <v>7326767</v>
+        <v>7326679</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
         <v>127074359</v>
       </c>
       <c r="B26" t="n">
-        <v>57817</v>
+        <v>57826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127079568</v>
+        <v>127075134</v>
       </c>
       <c r="B27" t="n">
-        <v>91319</v>
+        <v>79641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607570</v>
+        <v>607634</v>
       </c>
       <c r="R27" t="n">
-        <v>7326549</v>
+        <v>7326481</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127075134</v>
+        <v>127079568</v>
       </c>
       <c r="B28" t="n">
-        <v>79629</v>
+        <v>91341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607634</v>
+        <v>607570</v>
       </c>
       <c r="R28" t="n">
-        <v>7326481</v>
+        <v>7326549</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127076783</v>
+        <v>127079706</v>
       </c>
       <c r="B29" t="n">
-        <v>91284</v>
+        <v>91359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607730</v>
+        <v>607423</v>
       </c>
       <c r="R29" t="n">
-        <v>7326604</v>
+        <v>7326497</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127079706</v>
+        <v>127076783</v>
       </c>
       <c r="B30" t="n">
-        <v>91337</v>
+        <v>91306</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607423</v>
+        <v>607730</v>
       </c>
       <c r="R30" t="n">
-        <v>7326497</v>
+        <v>7326604</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,7 +3505,7 @@
         <v>127078742</v>
       </c>
       <c r="B31" t="n">
-        <v>92609</v>
+        <v>92631</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127079261</v>
+        <v>127078504</v>
       </c>
       <c r="B32" t="n">
-        <v>79629</v>
+        <v>79612</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607534</v>
+        <v>607646</v>
       </c>
       <c r="R32" t="n">
-        <v>7326663</v>
+        <v>7326785</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127078504</v>
+        <v>127079261</v>
       </c>
       <c r="B33" t="n">
-        <v>79600</v>
+        <v>79641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>607646</v>
+        <v>607534</v>
       </c>
       <c r="R33" t="n">
-        <v>7326785</v>
+        <v>7326663</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4325,7 +4325,7 @@
         <v>129188674</v>
       </c>
       <c r="B39" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4325,7 +4325,7 @@
         <v>129188674</v>
       </c>
       <c r="B39" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4325,7 +4325,7 @@
         <v>129188674</v>
       </c>
       <c r="B39" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4325,7 +4325,7 @@
         <v>129188674</v>
       </c>
       <c r="B39" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4325,7 +4325,7 @@
         <v>129188674</v>
       </c>
       <c r="B39" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4325,7 +4325,7 @@
         <v>129188674</v>
       </c>
       <c r="B39" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4325,7 +4325,7 @@
         <v>129188674</v>
       </c>
       <c r="B39" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -4325,7 +4325,7 @@
         <v>129188674</v>
       </c>
       <c r="B39" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 34810-2021 artfynd.xlsx
+++ b/artfynd/A 34810-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127076756</v>
+        <v>127078974</v>
       </c>
       <c r="B2" t="n">
-        <v>91359</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607755</v>
+        <v>607505</v>
       </c>
       <c r="R2" t="n">
-        <v>7326581</v>
+        <v>7326710</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127079280</v>
+        <v>128364510</v>
       </c>
       <c r="B3" t="n">
-        <v>91602</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607531</v>
+        <v>607558</v>
       </c>
       <c r="R3" t="n">
-        <v>7326670</v>
+        <v>7326436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,45 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127076668</v>
+        <v>127078636</v>
       </c>
       <c r="B4" t="n">
-        <v>79641</v>
+        <v>92183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607787</v>
+        <v>607586</v>
       </c>
       <c r="R4" t="n">
-        <v>7326543</v>
+        <v>7326861</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127074941</v>
+        <v>127079280</v>
       </c>
       <c r="B5" t="n">
-        <v>78429</v>
+        <v>92183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607611</v>
+        <v>607531</v>
       </c>
       <c r="R5" t="n">
-        <v>7326390</v>
+        <v>7326670</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127077017</v>
+        <v>129188285</v>
       </c>
       <c r="B6" t="n">
-        <v>79641</v>
+        <v>83299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Tjiärmadahkka, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607714</v>
+        <v>607624</v>
       </c>
       <c r="R6" t="n">
-        <v>7326595</v>
+        <v>7326586</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1141,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1142,28 +1155,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127078526</v>
+        <v>127078292</v>
       </c>
       <c r="B7" t="n">
-        <v>78429</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1185,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607630</v>
+        <v>607686</v>
       </c>
       <c r="R7" t="n">
-        <v>7326801</v>
+        <v>7326705</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127074380</v>
+        <v>127078508</v>
       </c>
       <c r="B8" t="n">
-        <v>78429</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1282,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607439</v>
+        <v>607646</v>
       </c>
       <c r="R8" t="n">
-        <v>7326243</v>
+        <v>7326785</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127074949</v>
+        <v>127078668</v>
       </c>
       <c r="B9" t="n">
-        <v>79641</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1379,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607611</v>
+        <v>607551</v>
       </c>
       <c r="R9" t="n">
-        <v>7326390</v>
+        <v>7326853</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,45 +1465,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127078636</v>
+        <v>128364532</v>
       </c>
       <c r="B10" t="n">
-        <v>91602</v>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607586</v>
+        <v>607627</v>
       </c>
       <c r="R10" t="n">
-        <v>7326861</v>
+        <v>7326556</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1516,12 +1530,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1548,10 +1572,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127078668</v>
+        <v>127079568</v>
       </c>
       <c r="B11" t="n">
-        <v>78690</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1583,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607551</v>
+        <v>607570</v>
       </c>
       <c r="R11" t="n">
-        <v>7326853</v>
+        <v>7326549</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,45 +1669,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127076330</v>
+        <v>127078849</v>
       </c>
       <c r="B12" t="n">
-        <v>79641</v>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607710</v>
+        <v>607506</v>
       </c>
       <c r="R12" t="n">
-        <v>7326472</v>
+        <v>7326767</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,45 +1766,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127074251</v>
+        <v>127078644</v>
       </c>
       <c r="B13" t="n">
-        <v>105482</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607381</v>
+        <v>607586</v>
       </c>
       <c r="R13" t="n">
-        <v>7326163</v>
+        <v>7326861</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,45 +1863,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127074519</v>
+        <v>127078742</v>
       </c>
       <c r="B14" t="n">
-        <v>80162</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607517</v>
+        <v>607552</v>
       </c>
       <c r="R14" t="n">
-        <v>7326285</v>
+        <v>7326830</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127079200</v>
+        <v>127076783</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607506</v>
+        <v>607730</v>
       </c>
       <c r="R15" t="n">
-        <v>7326696</v>
+        <v>7326604</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,54 +2057,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127075079</v>
+        <v>127079200</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607678</v>
+        <v>607506</v>
       </c>
       <c r="R16" t="n">
-        <v>7326420</v>
+        <v>7326696</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,10 +2154,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127078508</v>
+        <v>127074380</v>
       </c>
       <c r="B17" t="n">
-        <v>78690</v>
+        <v>78730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2165,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2189,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607646</v>
+        <v>607439</v>
       </c>
       <c r="R17" t="n">
-        <v>7326785</v>
+        <v>7326243</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2236,10 +2251,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127076482</v>
+        <v>127074651</v>
       </c>
       <c r="B18" t="n">
-        <v>78001</v>
+        <v>78730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2262,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607764</v>
+        <v>607532</v>
       </c>
       <c r="R18" t="n">
-        <v>7326485</v>
+        <v>7326271</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2333,45 +2348,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127078644</v>
+        <v>127074941</v>
       </c>
       <c r="B19" t="n">
-        <v>92631</v>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607586</v>
+        <v>607611</v>
       </c>
       <c r="R19" t="n">
-        <v>7326861</v>
+        <v>7326390</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2445,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127078292</v>
+        <v>127078526</v>
       </c>
       <c r="B20" t="n">
-        <v>78690</v>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2456,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2480,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607686</v>
+        <v>607630</v>
       </c>
       <c r="R20" t="n">
-        <v>7326705</v>
+        <v>7326801</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2527,10 +2542,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127078974</v>
+        <v>128364543</v>
       </c>
       <c r="B21" t="n">
-        <v>96711</v>
+        <v>78730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2538,34 +2553,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607505</v>
+        <v>607627</v>
       </c>
       <c r="R21" t="n">
-        <v>7326710</v>
+        <v>7326556</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2592,12 +2607,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2624,10 +2649,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076452</v>
+        <v>128364544</v>
       </c>
       <c r="B22" t="n">
-        <v>79641</v>
+        <v>78730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2635,34 +2660,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607721</v>
+        <v>607746</v>
       </c>
       <c r="R22" t="n">
-        <v>7326477</v>
+        <v>7326692</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2689,12 +2714,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2721,32 +2756,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127079093</v>
+        <v>127074704</v>
       </c>
       <c r="B23" t="n">
-        <v>105482</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607489</v>
+        <v>607555</v>
       </c>
       <c r="R23" t="n">
-        <v>7326681</v>
+        <v>7326287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,45 +2853,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127078849</v>
+        <v>127074949</v>
       </c>
       <c r="B24" t="n">
-        <v>91502</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607506</v>
+        <v>607611</v>
       </c>
       <c r="R24" t="n">
-        <v>7326767</v>
+        <v>7326390</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,10 +2950,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127079154</v>
+        <v>127075134</v>
       </c>
       <c r="B25" t="n">
-        <v>91359</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2926,21 +2961,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2950,10 +2985,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607496</v>
+        <v>607634</v>
       </c>
       <c r="R25" t="n">
-        <v>7326679</v>
+        <v>7326481</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,10 +3047,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127074359</v>
+        <v>127076330</v>
       </c>
       <c r="B26" t="n">
-        <v>57826</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,39 +3058,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607418</v>
+        <v>607710</v>
       </c>
       <c r="R26" t="n">
-        <v>7326232</v>
+        <v>7326472</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3144,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127075134</v>
+        <v>127076452</v>
       </c>
       <c r="B27" t="n">
-        <v>79641</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3149,10 +3179,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607634</v>
+        <v>607721</v>
       </c>
       <c r="R27" t="n">
-        <v>7326481</v>
+        <v>7326477</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,10 +3241,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127079568</v>
+        <v>127076668</v>
       </c>
       <c r="B28" t="n">
-        <v>91341</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3252,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3276,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607570</v>
+        <v>607787</v>
       </c>
       <c r="R28" t="n">
-        <v>7326549</v>
+        <v>7326543</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,10 +3338,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127079706</v>
+        <v>127077017</v>
       </c>
       <c r="B29" t="n">
-        <v>91359</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3349,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3373,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607423</v>
+        <v>607714</v>
       </c>
       <c r="R29" t="n">
-        <v>7326497</v>
+        <v>7326595</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,32 +3435,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127076783</v>
+        <v>127079261</v>
       </c>
       <c r="B30" t="n">
-        <v>91306</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3470,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607730</v>
+        <v>607534</v>
       </c>
       <c r="R30" t="n">
-        <v>7326604</v>
+        <v>7326663</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,45 +3532,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127078742</v>
+        <v>128364511</v>
       </c>
       <c r="B31" t="n">
-        <v>92631</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607552</v>
+        <v>607494</v>
       </c>
       <c r="R31" t="n">
-        <v>7326830</v>
+        <v>7326402</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3567,12 +3597,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3599,10 +3639,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127078504</v>
+        <v>128364512</v>
       </c>
       <c r="B32" t="n">
-        <v>79612</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,34 +3650,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607646</v>
+        <v>607775</v>
       </c>
       <c r="R32" t="n">
-        <v>7326785</v>
+        <v>7326678</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3664,12 +3704,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3696,32 +3746,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127079261</v>
+        <v>127074519</v>
       </c>
       <c r="B33" t="n">
-        <v>79641</v>
+        <v>80468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3781,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>607534</v>
+        <v>607517</v>
       </c>
       <c r="R33" t="n">
-        <v>7326663</v>
+        <v>7326285</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,10 +3843,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128364511</v>
+        <v>127076482</v>
       </c>
       <c r="B34" t="n">
-        <v>79743</v>
+        <v>78334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3804,34 +3854,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Korsträsk, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>607494</v>
+        <v>607764</v>
       </c>
       <c r="R34" t="n">
-        <v>7326402</v>
+        <v>7326485</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3858,22 +3908,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3900,10 +3940,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128364543</v>
+        <v>129211232</v>
       </c>
       <c r="B35" t="n">
-        <v>78527</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3911,34 +3951,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Korsträsk, Pi lm</t>
+          <t>Tjiärmadahkka , Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>607627</v>
+        <v>607765</v>
       </c>
       <c r="R35" t="n">
-        <v>7326556</v>
+        <v>7326469</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3965,22 +4009,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3995,60 +4044,68 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128364532</v>
+        <v>129188674</v>
       </c>
       <c r="B36" t="n">
-        <v>79203</v>
+        <v>57141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Korsträsk, Pi lm</t>
+          <t>Tjiärmadahkka , Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>607627</v>
+        <v>607648</v>
       </c>
       <c r="R36" t="n">
-        <v>7326556</v>
+        <v>7326543</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4072,22 +4129,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>18:07</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>18:07</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4102,22 +4149,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128364510</v>
+        <v>127074359</v>
       </c>
       <c r="B37" t="n">
-        <v>96882</v>
+        <v>58114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4125,34 +4172,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>607558</v>
+        <v>607418</v>
       </c>
       <c r="R37" t="n">
-        <v>7326436</v>
+        <v>7326232</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4179,22 +4231,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>18:12</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>18:12</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4221,10 +4263,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129188285</v>
+        <v>127075079</v>
       </c>
       <c r="B38" t="n">
-        <v>83031</v>
+        <v>58114</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4232,37 +4274,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tjiärmadahkka, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>607624</v>
+        <v>607678</v>
       </c>
       <c r="R38" t="n">
-        <v>7326586</v>
+        <v>7326420</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4289,12 +4337,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4303,75 +4351,71 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129188674</v>
+        <v>127078104</v>
       </c>
       <c r="B39" t="n">
-        <v>57092</v>
+        <v>58057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tjiärmadahkka , Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>607648</v>
+        <v>607755</v>
       </c>
       <c r="R39" t="n">
-        <v>7326543</v>
+        <v>7326703</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4395,12 +4439,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4415,61 +4459,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129211232</v>
+        <v>127074251</v>
       </c>
       <c r="B40" t="n">
-        <v>57735</v>
+        <v>106229</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tjiärmadahkka , Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>607765</v>
+        <v>607381</v>
       </c>
       <c r="R40" t="n">
-        <v>7326469</v>
+        <v>7326163</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4496,27 +4536,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4531,15 +4556,306 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127079093</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>607489</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7326681</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127074716</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>607555</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7326287</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127078504</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>607646</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7326785</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
